--- a/Documentacion/Testing/Copia de 1-MEC_TestingHito1.xlsx
+++ b/Documentacion/Testing/Copia de 1-MEC_TestingHito1.xlsx
@@ -2703,7 +2703,7 @@
         <v>45593</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="1"/>
